--- a/diseases/d178/2015-2019.xlsx
+++ b/diseases/d178/2015-2019.xlsx
@@ -10571,7 +10571,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -10970,7 +10970,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -12463,7 +12463,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -13261,7 +13261,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -14207,7 +14207,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -15153,7 +15153,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -15552,7 +15552,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -15951,7 +15951,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -16646,7 +16646,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -18538,7 +18538,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -18937,7 +18937,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -19336,7 +19336,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -19735,7 +19735,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -20829,7 +20829,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -21228,7 +21228,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -21627,7 +21627,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -22026,7 +22026,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -22721,7 +22721,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -23519,7 +23519,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -23918,7 +23918,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -24613,7 +24613,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -25012,7 +25012,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -25810,7 +25810,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -26209,7 +26209,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -27696,7 +27696,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -28095,7 +28095,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -28494,7 +28494,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -29189,7 +29189,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -29588,7 +29588,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -29987,7 +29987,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -30386,7 +30386,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -31081,7 +31081,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -31480,7 +31480,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -32278,7 +32278,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -32677,7 +32677,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -33372,7 +33372,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -33771,7 +33771,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -34170,7 +34170,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -34569,7 +34569,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -35264,7 +35264,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -35663,7 +35663,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -36062,7 +36062,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -36461,7 +36461,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -37156,7 +37156,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -37555,7 +37555,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -37954,7 +37954,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -38353,7 +38353,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -38752,7 +38752,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -39447,7 +39447,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -39846,7 +39846,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -40245,7 +40245,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -40644,7 +40644,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -41339,7 +41339,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -41738,7 +41738,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -42137,7 +42137,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -42536,7 +42536,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -43083,7 +43083,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -43630,7 +43630,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -44029,7 +44029,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -44428,7 +44428,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -44827,7 +44827,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -45522,7 +45522,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -46320,7 +46320,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -46719,7 +46719,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -47414,7 +47414,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -47813,7 +47813,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -48212,7 +48212,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -48611,7 +48611,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -49158,7 +49158,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -49705,7 +49705,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -50104,7 +50104,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -50503,7 +50503,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -50902,7 +50902,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
